--- a/DSA_15_Patterns_150_Easy_LeetCode_Questions.xlsx
+++ b/DSA_15_Patterns_150_Easy_LeetCode_Questions.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="305">
   <si>
     <t xml:space="preserve">Pattern</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sort Array By Parity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solved on 21.09.2026</t>
   </si>
   <si>
     <t xml:space="preserve">941</t>
@@ -1641,7 +1644,9 @@
       <c r="F8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
@@ -1651,18 +1656,20 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
@@ -1672,10 +1679,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>10</v>
@@ -1693,10 +1700,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>10</v>
@@ -1708,7 +1715,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>1</v>
@@ -1729,16 +1736,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>10</v>
@@ -1750,16 +1757,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>10</v>
@@ -1771,16 +1778,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>10</v>
@@ -1792,16 +1799,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>10</v>
@@ -1813,16 +1820,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>10</v>
@@ -1834,16 +1841,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>10</v>
@@ -1855,16 +1862,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>10</v>
@@ -1876,16 +1883,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>10</v>
@@ -1897,16 +1904,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>10</v>
@@ -1918,16 +1925,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>10</v>
@@ -1939,16 +1946,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>10</v>
@@ -1960,16 +1967,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>10</v>
@@ -1981,16 +1988,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>10</v>
@@ -2002,16 +2009,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>10</v>
@@ -2023,16 +2030,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>10</v>
@@ -2044,16 +2051,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>10</v>
@@ -2065,16 +2072,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>10</v>
@@ -2086,16 +2093,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>10</v>
@@ -2107,16 +2114,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>10</v>
@@ -2128,16 +2135,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>10</v>
@@ -2149,16 +2156,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>10</v>
@@ -2170,16 +2177,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>10</v>
@@ -2191,16 +2198,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>10</v>
@@ -2212,16 +2219,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>10</v>
@@ -2233,16 +2240,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>10</v>
@@ -2254,16 +2261,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>10</v>
@@ -2275,16 +2282,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>10</v>
@@ -2296,16 +2303,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>10</v>
@@ -2317,16 +2324,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>10</v>
@@ -2338,16 +2345,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>10</v>
@@ -2359,16 +2366,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>10</v>
@@ -2380,16 +2387,16 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>10</v>
@@ -2401,16 +2408,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>10</v>
@@ -2422,16 +2429,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>10</v>
@@ -2443,16 +2450,16 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>10</v>
@@ -2464,16 +2471,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>10</v>
@@ -2485,16 +2492,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>10</v>
@@ -2506,16 +2513,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>10</v>
@@ -2527,16 +2534,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>10</v>
@@ -2548,16 +2555,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B52" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>10</v>
@@ -2569,16 +2576,16 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B53" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>10</v>
@@ -2590,16 +2597,16 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B54" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>10</v>
@@ -2611,16 +2618,16 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>10</v>
@@ -2632,16 +2639,16 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B56" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>10</v>
@@ -2653,16 +2660,16 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>10</v>
@@ -2674,16 +2681,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B58" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>10</v>
@@ -2695,16 +2702,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B59" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>10</v>
@@ -2716,16 +2723,16 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B60" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>10</v>
@@ -2737,16 +2744,16 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B61" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>10</v>
@@ -2758,16 +2765,16 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B62" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>10</v>
@@ -2779,16 +2786,16 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B63" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>10</v>
@@ -2800,16 +2807,16 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B64" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>10</v>
@@ -2821,16 +2828,16 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B65" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>10</v>
@@ -2842,16 +2849,16 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B66" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>10</v>
@@ -2863,16 +2870,16 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>10</v>
@@ -2884,16 +2891,16 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>10</v>
@@ -2905,16 +2912,16 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>10</v>
@@ -2926,16 +2933,16 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>10</v>
@@ -2947,16 +2954,16 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>10</v>
@@ -2968,16 +2975,16 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B72" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>10</v>
@@ -2989,16 +2996,16 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B73" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>10</v>
@@ -3010,16 +3017,16 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B74" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>10</v>
@@ -3031,16 +3038,16 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B75" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>10</v>
@@ -3052,16 +3059,16 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B76" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>10</v>
@@ -3073,16 +3080,16 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B77" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>10</v>
@@ -3094,16 +3101,16 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B78" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>10</v>
@@ -3115,16 +3122,16 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B79" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>10</v>
@@ -3136,16 +3143,16 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B80" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>10</v>
@@ -3157,16 +3164,16 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B81" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>10</v>
@@ -3178,16 +3185,16 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B82" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>10</v>
@@ -3199,16 +3206,16 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B83" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>10</v>
@@ -3220,16 +3227,16 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B84" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>10</v>
@@ -3241,16 +3248,16 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B85" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>10</v>
@@ -3262,16 +3269,16 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B86" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>10</v>
@@ -3283,16 +3290,16 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B87" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>10</v>
@@ -3304,16 +3311,16 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B88" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>10</v>
@@ -3325,16 +3332,16 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B89" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E89" s="5" t="s">
         <v>10</v>
@@ -3346,16 +3353,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B90" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>10</v>
@@ -3367,16 +3374,16 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>10</v>
@@ -3388,16 +3395,16 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B92" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>10</v>
@@ -3409,16 +3416,16 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B93" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>10</v>
@@ -3430,16 +3437,16 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B94" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>10</v>
@@ -3451,16 +3458,16 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>10</v>
@@ -3472,16 +3479,16 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B96" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>10</v>
@@ -3493,16 +3500,16 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B97" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>10</v>
@@ -3514,16 +3521,16 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>10</v>
@@ -3535,16 +3542,16 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>10</v>
@@ -3556,16 +3563,16 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B100" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>10</v>
@@ -3577,16 +3584,16 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B101" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>10</v>
@@ -3598,16 +3605,16 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B102" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E102" s="5" t="s">
         <v>10</v>
@@ -3619,16 +3626,16 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B103" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E103" s="5" t="s">
         <v>10</v>
@@ -3640,16 +3647,16 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B104" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>10</v>
@@ -3661,16 +3668,16 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B105" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E105" s="5" t="s">
         <v>10</v>
@@ -3682,16 +3689,16 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B106" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E106" s="5" t="s">
         <v>10</v>
@@ -3703,16 +3710,16 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B107" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E107" s="5" t="s">
         <v>10</v>
@@ -3724,16 +3731,16 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B108" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E108" s="5" t="s">
         <v>10</v>
@@ -3745,16 +3752,16 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B109" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>10</v>
@@ -3766,16 +3773,16 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B110" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>10</v>
@@ -3787,16 +3794,16 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B111" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E111" s="5" t="s">
         <v>10</v>
@@ -3808,16 +3815,16 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B112" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E112" s="5" t="s">
         <v>10</v>
@@ -3829,16 +3836,16 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B113" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>10</v>
@@ -3850,16 +3857,16 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B114" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E114" s="5" t="s">
         <v>10</v>
@@ -3871,16 +3878,16 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B115" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>10</v>
@@ -3892,16 +3899,16 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B116" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>10</v>
@@ -3913,16 +3920,16 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B117" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>10</v>
@@ -3934,16 +3941,16 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B118" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>10</v>
@@ -3955,16 +3962,16 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B119" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E119" s="5" t="s">
         <v>10</v>
@@ -3976,16 +3983,16 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B120" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>10</v>
@@ -3997,16 +4004,16 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B121" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E121" s="5" t="s">
         <v>10</v>
@@ -4018,16 +4025,16 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B122" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>10</v>
@@ -4039,16 +4046,16 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B123" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>10</v>
@@ -4060,16 +4067,16 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B124" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>10</v>
@@ -4081,16 +4088,16 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B125" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>10</v>
@@ -4102,16 +4109,16 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B126" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E126" s="5" t="s">
         <v>10</v>
@@ -4123,16 +4130,16 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B127" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>10</v>
@@ -4144,16 +4151,16 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B128" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E128" s="5" t="s">
         <v>10</v>
@@ -4165,16 +4172,16 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B129" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E129" s="5" t="s">
         <v>10</v>
@@ -4186,16 +4193,16 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B130" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E130" s="5" t="s">
         <v>10</v>
@@ -4207,16 +4214,16 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B131" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>10</v>
@@ -4228,16 +4235,16 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B132" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E132" s="5" t="s">
         <v>10</v>
@@ -4249,16 +4256,16 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B133" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E133" s="5" t="s">
         <v>10</v>
@@ -4270,16 +4277,16 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B134" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E134" s="5" t="s">
         <v>10</v>
@@ -4291,16 +4298,16 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B135" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>10</v>
@@ -4312,16 +4319,16 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B136" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>10</v>
@@ -4333,16 +4340,16 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B137" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>10</v>
@@ -4354,16 +4361,16 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B138" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E138" s="5" t="s">
         <v>10</v>
@@ -4375,16 +4382,16 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B139" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>10</v>
@@ -4396,16 +4403,16 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B140" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>10</v>
@@ -4417,16 +4424,16 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B141" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E141" s="5" t="s">
         <v>10</v>
@@ -4438,16 +4445,16 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B142" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>10</v>
@@ -4459,16 +4466,16 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B143" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>10</v>
@@ -4480,16 +4487,16 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B144" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E144" s="5" t="s">
         <v>10</v>
@@ -4501,16 +4508,16 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B145" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>10</v>
@@ -4522,16 +4529,16 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B146" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E146" s="5" t="s">
         <v>10</v>
@@ -4543,16 +4550,16 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B147" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E147" s="5" t="s">
         <v>10</v>
@@ -4564,16 +4571,16 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B148" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E148" s="5" t="s">
         <v>10</v>
@@ -4585,16 +4592,16 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B149" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>10</v>
@@ -4606,16 +4613,16 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B150" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>10</v>
@@ -4627,16 +4634,16 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B151" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E151" s="5" t="s">
         <v>10</v>
@@ -4700,10 +4707,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -4718,10 +4725,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -4736,10 +4743,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -4754,10 +4761,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -4772,10 +4779,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -4790,10 +4797,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -4808,10 +4815,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -4826,10 +4833,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -4844,10 +4851,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -4862,10 +4869,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -4929,10 +4936,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -4947,10 +4954,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -4965,10 +4972,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -4983,10 +4990,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -5001,10 +5008,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -5019,10 +5026,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -5037,10 +5044,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -5055,10 +5062,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -5073,10 +5080,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -5091,10 +5098,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -5158,10 +5165,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -5176,10 +5183,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -5194,10 +5201,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -5212,10 +5219,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -5230,10 +5237,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -5248,10 +5255,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -5266,10 +5273,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -5284,10 +5291,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -5302,10 +5309,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -5320,10 +5327,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -5387,10 +5394,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -5405,10 +5412,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -5423,10 +5430,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -5441,10 +5448,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -5459,10 +5466,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -5477,10 +5484,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -5495,10 +5502,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -5513,10 +5520,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -5531,10 +5538,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -5549,10 +5556,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -5616,10 +5623,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -5634,10 +5641,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -5652,10 +5659,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -5670,10 +5677,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -5688,10 +5695,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -5706,10 +5713,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -5724,10 +5731,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -5742,10 +5749,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -5760,10 +5767,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -5778,10 +5785,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -5845,10 +5852,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -5863,10 +5870,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -5881,10 +5888,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -5899,10 +5906,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -5917,10 +5924,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -5935,10 +5942,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -5953,10 +5960,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -5971,10 +5978,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -5989,10 +5996,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -6007,10 +6014,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -6074,10 +6081,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -6092,10 +6099,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -6110,10 +6117,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -6128,10 +6135,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -6146,10 +6153,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -6164,10 +6171,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -6182,10 +6189,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -6200,10 +6207,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -6218,10 +6225,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -6236,10 +6243,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -6303,10 +6310,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -6321,10 +6328,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -6339,10 +6346,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -6357,10 +6364,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -6375,10 +6382,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -6393,10 +6400,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -6411,10 +6418,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -6429,10 +6436,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -6447,10 +6454,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -6465,10 +6472,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -6507,19 +6514,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6536,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6544,7 +6551,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>10</v>
@@ -6553,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6561,7 +6568,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>10</v>
@@ -6570,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6578,7 +6585,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>10</v>
@@ -6587,7 +6594,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6595,7 +6602,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>10</v>
@@ -6604,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6612,7 +6619,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>10</v>
@@ -6621,7 +6628,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6629,7 +6636,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>10</v>
@@ -6638,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6646,7 +6653,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>10</v>
@@ -6655,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6663,7 +6670,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>10</v>
@@ -6672,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6680,7 +6687,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>10</v>
@@ -6689,7 +6696,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6697,7 +6704,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>10</v>
@@ -6706,7 +6713,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6714,7 +6721,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>10</v>
@@ -6723,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6731,7 +6738,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>10</v>
@@ -6740,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6748,7 +6755,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>10</v>
@@ -6757,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6765,7 +6772,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>10</v>
@@ -6774,7 +6781,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -6957,10 +6964,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -6975,10 +6982,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -6993,10 +7000,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -7078,10 +7085,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -7096,10 +7103,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -7114,10 +7121,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -7132,10 +7139,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -7150,10 +7157,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -7168,10 +7175,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -7186,10 +7193,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -7204,10 +7211,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -7222,10 +7229,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -7289,10 +7296,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -7307,10 +7314,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -7325,10 +7332,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -7343,10 +7350,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -7361,10 +7368,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -7379,10 +7386,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -7397,10 +7404,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -7415,10 +7422,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -7433,10 +7440,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -7451,10 +7458,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -7518,10 +7525,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -7536,10 +7543,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -7554,10 +7561,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -7572,10 +7579,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -7590,10 +7597,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -7608,10 +7615,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -7626,10 +7633,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -7644,10 +7651,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -7662,10 +7669,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -7680,10 +7687,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -7747,10 +7754,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -7765,10 +7772,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -7783,10 +7790,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -7801,10 +7808,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -7819,10 +7826,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -7837,10 +7844,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -7855,10 +7862,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -7873,10 +7880,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -7891,10 +7898,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -7909,10 +7916,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -7976,10 +7983,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -7994,10 +8001,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -8012,10 +8019,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -8030,10 +8037,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -8048,10 +8055,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -8066,10 +8073,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -8084,10 +8091,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -8102,10 +8109,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -8120,10 +8127,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -8138,10 +8145,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -8205,10 +8212,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
@@ -8223,10 +8230,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -8241,10 +8248,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -8259,10 +8266,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -8277,10 +8284,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -8295,10 +8302,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
@@ -8313,10 +8320,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -8331,10 +8338,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -8349,10 +8356,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -8367,10 +8374,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>10</v>
